--- a/tests/data_golden/links.expected.xlsx
+++ b/tests/data_golden/links.expected.xlsx
@@ -58,7 +58,7 @@
     <t>Docs</t>
   </si>
   <si>
-    <t>See: Details</t>
+    <t xml:space="preserve">See: Details</t>
   </si>
   <si>
     <t>t</t>
